--- a/data/image_scenario.xlsx
+++ b/data/image_scenario.xlsx
@@ -1,166 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20373"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\veo3\project\lion\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA615B0F-84E6-4B1F-8722-099293EA7F2B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Script" sheetId="4" r:id="rId1"/>
-    <sheet name="Templates" sheetId="1" r:id="rId2"/>
+    <sheet name="Script" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Templates" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
-  <si>
-    <t>template_key</t>
-  </si>
-  <si>
-    <t>template_value</t>
-  </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>Mẫu_Ảnh_Ngang_Anime</t>
-  </si>
-  <si>
-    <t>Anime style illustration of {0} wearing {1.0}, trending on pixiv, highly detailed --ar 16:9</t>
-  </si>
-  <si>
-    <t>Chỉ dùng {0} và {1}, bỏ qua ảnh tham chiếu</t>
-  </si>
-  <si>
-    <t>Mẫu_Ảnh_Ngang_Cinematic</t>
-  </si>
-  <si>
-    <t>"A cinematic scene of {1.0} fighting against {1.1} inside {2.0}, action: {0}"</t>
-  </si>
-  <si>
-    <t>Dùng đầy đủ cả 3 tham số đầu vào</t>
-  </si>
-  <si>
-    <t>NhanVat_and_Action</t>
-  </si>
-  <si>
-    <t>"{1.0}   {0}"</t>
-  </si>
-  <si>
-    <t>scene_id</t>
-  </si>
-  <si>
-    <t>prompt_core</t>
-  </si>
-  <si>
-    <t>character_list</t>
-  </si>
-  <si>
-    <t>reference_list</t>
-  </si>
-  <si>
-    <t>final_prompt</t>
-  </si>
-  <si>
-    <t>status_time</t>
-  </si>
-  <si>
-    <t>output_id</t>
-  </si>
-  <si>
-    <t>file_name</t>
-  </si>
-  <si>
-    <t>image_1</t>
-  </si>
-  <si>
-    <t>reading book</t>
-  </si>
-  <si>
-    <t>nvHoang</t>
-  </si>
-  <si>
-    <t>scena_1 reading book"</t>
-  </si>
-  <si>
-    <t>image_2</t>
-  </si>
-  <si>
-    <t>close eyes</t>
-  </si>
-  <si>
-    <t>scena_1</t>
-  </si>
-  <si>
-    <t>scena_2 close eyes"</t>
-  </si>
-  <si>
-    <t>image_3</t>
-  </si>
-  <si>
-    <t>open one eye</t>
-  </si>
-  <si>
-    <t>scena_2</t>
-  </si>
-  <si>
-    <t>scena_3 open one eye"</t>
-  </si>
-  <si>
-    <t>image_4</t>
-  </si>
-  <si>
-    <t>open the eyes</t>
-  </si>
-  <si>
-    <t>scena_3</t>
-  </si>
-  <si>
-    <t>scena_4 open the eyes"</t>
-  </si>
-  <si>
-    <t>image_5</t>
-  </si>
-  <si>
-    <t>smile</t>
-  </si>
-  <si>
-    <t>scena_4</t>
-  </si>
-  <si>
-    <t>scena_5 smile"</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -194,24 +67,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -499,145 +431,139 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" customWidth="1"/>
-    <col min="5" max="5" width="29.28515625" customWidth="1"/>
-    <col min="6" max="6" width="36.42578125" customWidth="1"/>
-    <col min="7" max="7" width="33.7109375" customWidth="1"/>
-    <col min="8" max="8" width="25.28515625" customWidth="1"/>
-    <col min="9" max="9" width="22.5703125" customWidth="1"/>
+    <col width="16.28515625" customWidth="1" min="1" max="1"/>
+    <col width="20" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="54.7109375" customWidth="1" min="3" max="3"/>
+    <col width="18.85546875" customWidth="1" min="4" max="4"/>
+    <col width="29.28515625" customWidth="1" min="5" max="5"/>
+    <col width="36.42578125" customWidth="1" min="6" max="6"/>
+    <col width="33.7109375" customWidth="1" min="7" max="7"/>
+    <col width="25.28515625" customWidth="1" min="8" max="8"/>
+    <col width="22.5703125" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" t="s">
-        <v>38</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>scene_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>template_key</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>prompt_core</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>character_list</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>reference_list</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>final_prompt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>status_time</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>output_id</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>file_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mage_1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>On the open grasslands, everything appears calm.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>mage_1 On the open grasslands, everything appears calm.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>mage_1 On the open g</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mage_2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A small herd of antelope grazes peacefully</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>mage_1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>mage_2 A small herd of antelope grazes peacefully</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>mage_2 A small herd</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -646,53 +572,91 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="114.42578125" customWidth="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="114.42578125" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>template_key</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>template_value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mẫu_Ảnh_Ngang_Anime</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anime style illustration of {0} wearing {1.0}, trending on pixiv, highly detailed --ar 16:9</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Chỉ dùng {0} và {1}, bỏ qua ảnh tham chiếu</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mẫu_Ảnh_Ngang_Cinematic</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>"A cinematic scene of {1.0} fighting against {1.1} inside {2.0}, action: {0}"</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dùng đầy đủ cả 3 tham số đầu vào</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NhanVat_and_Action</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>"{1.0}   {0}"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>{0}</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/image_scenario.xlsx
+++ b/data/image_scenario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\veo3\project\lion\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B1B1E3-B1EF-4ECE-AFE8-80478DA04A56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF25EFB-C201-438C-ACF2-A611193F3D3B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
